--- a/data/trans_bre/IP16B02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16B02-Provincia-trans_bre.xlsx
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 29,94</t>
+          <t>-16,32; 24,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-51,04; 15,08</t>
+          <t>-52,17; 12,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,19 +654,19 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 44,04</t>
+          <t>-16,76; 32,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-56,01; 20,52</t>
+          <t>-60,0; 13,65</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 10,83</t>
+          <t>-27,47; 11,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 0,0</t>
+          <t>-34,84; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,19 +734,19 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 12,22</t>
+          <t>-28,78; 12,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 0,0</t>
+          <t>-34,84; 0,0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-34,99; 14,62</t>
+          <t>-29,82; 14,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 17,65</t>
+          <t>-31,34; 17,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,71; 0,0</t>
+          <t>-53,74; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 54,24</t>
+          <t>-20,3; 51,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,09; -5,68</t>
+          <t>-40,63; -5,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,71; 0,0</t>
+          <t>-53,74; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 164,76</t>
+          <t>-22,32; 128,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,09; -5,68</t>
+          <t>-40,63; -5,33</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 46,98</t>
+          <t>-30,64; 46,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 130,67</t>
+          <t>-34,46; 129,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 82,92</t>
+          <t>-10,78; 83,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,78</t>
+          <t>0,0; 37,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 488,45</t>
+          <t>-13,28; 491,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,73</t>
+          <t>0,0; 60,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-28,74; 20,63</t>
+          <t>-29,02; 25,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-50,78; -10,4</t>
+          <t>-50,94; -10,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-51,78; 18,54</t>
+          <t>-49,11; 26,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 27,73</t>
+          <t>-30,22; 28,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-50,78; -10,4</t>
+          <t>-50,94; -10,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-57,86; 30,98</t>
+          <t>-55,98; 44,5</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,85; -7,72</t>
+          <t>-59,42; -3,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,46; 22,52</t>
+          <t>-49,88; 20,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,02</t>
+          <t>0,0; 25,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-66,68; -9,89</t>
+          <t>-65,64; -4,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 32,0</t>
+          <t>-57,28; 30,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,17</t>
+          <t>0,0; 34,72</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 3,06</t>
+          <t>-21,95; 2,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 2,94</t>
+          <t>-16,6; 3,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 1,57</t>
+          <t>-17,29; 2,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 3,62</t>
+          <t>-24,49; 2,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 3,24</t>
+          <t>-18,43; 3,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 1,78</t>
+          <t>-18,78; 3,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16B02-Provincia-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 24,43</t>
+          <t>-17,04; 23,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-52,17; 12,2</t>
+          <t>-47,56; 12,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 32,7</t>
+          <t>-17,49; 31,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,0; 13,65</t>
+          <t>-50,71; 15,37</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,47; 11,16</t>
+          <t>-28,99; 11,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 0,0</t>
+          <t>-35,22; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,78; 12,53</t>
+          <t>-31,46; 12,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 0,0</t>
+          <t>-35,22; 0,0</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 14,57</t>
+          <t>-34,25; 14,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-31,34; 17,49</t>
+          <t>-34,43; 17,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,74; 0,0</t>
+          <t>-47,33; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 51,85</t>
+          <t>-23,68; 53,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,63; -5,33</t>
+          <t>-39,0; -5,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,74; 0,0</t>
+          <t>-47,33; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 128,74</t>
+          <t>-23,68; 134,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,63; -5,33</t>
+          <t>-39,0; -5,04</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 46,49</t>
+          <t>-26,02; 47,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-34,46; 129,24</t>
+          <t>-29,34; 145,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 83,02</t>
+          <t>-10,76; 82,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,79</t>
+          <t>0,0; 37,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 491,02</t>
+          <t>-13,87; 491,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,74</t>
+          <t>0,0; 60,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 25,27</t>
+          <t>-29,14; 24,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-50,94; -10,23</t>
+          <t>-54,87; -11,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 26,22</t>
+          <t>-50,98; 21,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-30,22; 28,54</t>
+          <t>-32,15; 31,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-50,94; -10,23</t>
+          <t>-54,87; -11,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-55,98; 44,5</t>
+          <t>-54,74; 36,38</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,42; -3,67</t>
+          <t>-60,29; -5,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,88; 20,12</t>
+          <t>-50,19; 19,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,77</t>
+          <t>0,0; 31,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-65,64; -4,91</t>
+          <t>-67,11; -7,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,28; 30,65</t>
+          <t>-60,43; 29,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,72</t>
+          <t>0,0; 46,77</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 2,46</t>
+          <t>-21,51; 2,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 3,08</t>
+          <t>-16,78; 2,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 2,8</t>
+          <t>-17,94; 2,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,49; 2,94</t>
+          <t>-23,73; 2,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 3,31</t>
+          <t>-18,46; 2,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 3,19</t>
+          <t>-19,2; 2,48</t>
         </is>
       </c>
     </row>
